--- a/content/tz-samoe-dlinnoe-slovo.xlsx
+++ b/content/tz-samoe-dlinnoe-slovo.xlsx
@@ -1692,7 +1692,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Инфографика, 1200×~580</t>
+          <t>Инфографика, 1200×636</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>40 000–45 000 с учётом прироста ~630 знаков после адресов Tilda</t>
+          <t>норма 40 000–45 000 с учётом прироста ~630 знаков; факт 44 051, после адресов ≈ 44 680</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>норма 26–31 %; факт 27,3 %</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>36–40 %</t>
+          <t>норма 36–40 %; факт 39,5 %</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>открывающих = закрывающих</t>
+          <t>21 / 21</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>нарушений по чужим адресам 0</t>
+          <t>0 нарушений по чужим адресам; две ожидаемые строки про временный свой адрес</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>0 — машинная проверка фрагментами по 60 знаков, особенно против «Интересных фактов», «Идиом», «Букв или иероглифов» и «Каких букв»</t>
+          <t>0 содержательных — машинная проверка фрагментами по 60 знаков по всем 152 страницам; совпадает только служебный хвост CTA</t>
         </is>
       </c>
     </row>
